--- a/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
+++ b/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
@@ -1068,6 +1068,11 @@
           <t>01:36:38.000</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1460,6 +1465,11 @@
           <t>01:38:57.000</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3636,6 +3646,11 @@
           <t>01:24:27.000</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>42352</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3827,6 +3842,11 @@
           <t>01:27:25.000</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>45286</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3889,6 +3909,11 @@
           <t>01:27:36.000</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>49452</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3951,6 +3976,11 @@
           <t>01:28:51.000</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4204,6 +4234,11 @@
           <t>01:31:03.000</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>54948</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4390,6 +4425,11 @@
           <t>01:34:24.000</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>49718</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4638,6 +4678,11 @@
           <t>01:38:41.000</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>49154</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4700,6 +4745,11 @@
           <t>01:43:59.000</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>48866</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4823,6 +4873,11 @@
           <t>01:25:57.000</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>45127</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4885,6 +4940,11 @@
           <t>01:25:58.000</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>49464</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4947,6 +5007,11 @@
           <t>01:26:10.000</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5200,6 +5265,11 @@
           <t>01:28:40.000</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5262,6 +5332,11 @@
           <t>01:28:54.000</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>49516</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6494,6 +6569,11 @@
           <t>01:44:53.000</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7780,6 +7860,11 @@
           <t>01:52:06.000</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>72778</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8373,6 +8458,11 @@
           <t>01:51:56.000</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9909,6 +9999,11 @@
       <c r="L147" t="n">
         <v>158</v>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>120791</t>
+        </is>
+      </c>
       <c r="X147" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -10841,6 +10936,11 @@
           <t>01:32:19.000</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>48168</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11171,6 +11271,11 @@
           <t>49777</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>49779</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11357,6 +11462,11 @@
           <t>01:37:10.000</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>134446</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11419,6 +11529,11 @@
           <t>01:37:11.000</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>49745</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11481,6 +11596,11 @@
           <t>01:37:17.000</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>141785</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11788,6 +11908,11 @@
       <c r="L176" t="n">
         <v>207</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>48944</t>
+        </is>
+      </c>
       <c r="X176" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -12788,6 +12913,11 @@
           <t>01:29:50.000</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>129379</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12912,6 +13042,11 @@
           <t>01:30:57.000</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>54948</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13175,6 +13310,11 @@
           <t>01:21:40.000</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15257,6 +15397,11 @@
           <t>02:24:37.000</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>53061</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15631,6 +15776,11 @@
           <t>02:06:35.000</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15961,6 +16111,11 @@
           <t>02:11:05.000</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17826,6 +17981,11 @@
           <t>02:16:04.000</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17888,6 +18048,11 @@
           <t>02:16:18.000</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>42769</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18270,6 +18435,11 @@
           <t>02:20:31.000</t>
         </is>
       </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>151199</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19789,6 +19959,16 @@
           <t>02:00:24.000</t>
         </is>
       </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -20500,6 +20680,11 @@
           <t>01:57:17.000</t>
         </is>
       </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>48163</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -20979,6 +21164,11 @@
           <t>02:07:18.000</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>172027</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -21592,6 +21782,11 @@
           <t>02:04:01.000</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S326" t="inlineStr">
         <is>
           <t>49664</t>
@@ -22359,6 +22554,11 @@
           <t>02:12:59.000</t>
         </is>
       </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -22797,6 +22997,11 @@
           <t>35385</t>
         </is>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>54196</t>
+        </is>
+      </c>
       <c r="X344" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -22858,6 +23063,11 @@
           <t>48494</t>
         </is>
       </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>88454</t>
+        </is>
+      </c>
       <c r="X345" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -23101,6 +23311,11 @@
       </c>
       <c r="L349" t="n">
         <v>405</v>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -23251,7 +23466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27544,6 +27759,864 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>42352</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Katrine Graesboll</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CHRISTENSEN</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>42769</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Celso</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>DIAS DE OLIVEIRA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>45127</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Kristof</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>KHAUT</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>45286</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Marte</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SOLHAUG</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>MYSAK</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CAFFA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>48168</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Mykhailo</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>PRYKHODKO</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>48866</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>MALINEN</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>49154</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Maija</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SAALASTI</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>49452</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Estefania</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>MASSAGUES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>49464</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Patryk</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>GLUZA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>49516</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>URSULA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Levente</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>BALLA</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Tamas</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>49718</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nikola</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ZATLKAJOVA</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>49745</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nils</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>THORESSON</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Emil</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TORSTENSSON</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>49779</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Martin Florian</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SCHUBERT</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>KOSTROMITINA</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>MIRONCHENKO</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Carlo</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TACCHINI</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>53061</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>MCLAIN</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>54196</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>DOUX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>54948</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>JOHANSSON</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>72778</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Dmytro</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ZAGNII</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>88454</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SIMMONS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>120791</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>BUGGY</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>129379</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>HERNANDEZ VELLISCA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>134446</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Coran</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>LONGWOOD</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>141785</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PRATO</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>151199</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Borys</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MARKIN</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>172027</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>KRUGLIAKOV</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
+++ b/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
@@ -6571,7 +6571,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>48165</t>
         </is>
       </c>
     </row>
@@ -27762,17 +27762,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Katrine Graesboll</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SOUSA</t>
+          <t>CHRISTENSEN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -27784,39 +27784,39 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>42352</t>
+          <t>42769</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Katrine Graesboll</t>
+          <t>Celso</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CHRISTENSEN</t>
+          <t>DIAS DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>45127</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Celso</t>
+          <t>Kristof</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DIAS DE OLIVEIRA JUNIOR</t>
+          <t>KHAUT</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -27828,61 +27828,61 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>45286</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Kristof</t>
+          <t>Marte</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>KHAUT</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>45352</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Marte</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>MYSAK</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MYSAK</t>
+          <t>CAFFA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -27894,17 +27894,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>48168</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CAFFA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27916,17 +27916,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>48188</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Mykhailo</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PRYKHODKO</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27938,39 +27938,39 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>48188</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Mykhailo</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PRYKHODKO</t>
+          <t>MALINEN</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>48866</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Maija</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MALINEN</t>
+          <t>SAALASTI</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27982,17 +27982,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Maija</t>
+          <t>Estefania</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SAALASTI</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -28004,17 +28004,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>49452</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Estefania</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>MASSAGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -28026,39 +28026,39 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Patryk</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MASSAGUES</t>
+          <t>GLUZA</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Patryk</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>GLUZA</t>
+          <t>URSULA</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -28070,17 +28070,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Mads Brandt</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>URSULA</t>
+          <t>PEDERSEN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28092,17 +28092,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>49654</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Mads Brandt</t>
+          <t>Levente</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PEDERSEN</t>
+          <t>BALLA</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28114,17 +28114,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>49654</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Levente</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BALLA</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28136,17 +28136,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>49667</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Tamas</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>KISS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28158,61 +28158,61 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>49667</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tamas</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>KISS</t>
+          <t>ZATLKAJOVA</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Joep</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ZATLKAJOVA</t>
+          <t>BAKEL VAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Joep</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BAKEL VAN</t>
+          <t>THORESSON</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28224,17 +28224,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>THORESSON</t>
+          <t>TORSTENSSON</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28246,17 +28246,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Martin Florian</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TORSTENSSON</t>
+          <t>SCHUBERT</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28268,193 +28268,193 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>49779</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Martin Florian</t>
+          <t>Alena</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SCHUBERT</t>
+          <t>KOSTROMITINA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>49833</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Alena</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>KOSTROMITINA</t>
+          <t>ERLINEKOV</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ERLINEKOV</t>
+          <t>MIRONCHENKO</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>49835</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MIRONCHENKO</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>MCLAIN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>54196</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>MCLAIN</t>
+          <t>DOUX</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>54948</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Johanna</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DOUX</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Johanna</t>
+          <t>Dmytro</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>ZAGNII</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>72778</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dmytro</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ZAGNII</t>
+          <t>SIMMONS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -28466,17 +28466,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>120791</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SIMMONS</t>
+          <t>BUGGY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -28488,61 +28488,61 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>120791</t>
+          <t>129379</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Marian</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>BUGGY</t>
+          <t>HERNANDEZ VELLISCA</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>129379</t>
+          <t>134446</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Coran</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HERNANDEZ VELLISCA</t>
+          <t>LONGWOOD</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Coran</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>LONGWOOD</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -28554,17 +28554,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>141785</t>
+          <t>151199</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Gene</t>
+          <t>Borys</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>MARKIN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28576,17 +28576,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>151199</t>
+          <t>172027</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Borys</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>MARKIN</t>
+          <t>KRUGLIAKOV</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28598,22 +28598,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>172027</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>KRUGLIAKOV</t>
+          <t>MARINHO SOUSA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>

--- a/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
+++ b/events/Copenhagen_2013_MAR/Copenhagen_2013_MAR_Results.xlsx
@@ -22621,6 +22621,11 @@
           <t>02:13:09.000</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>161210</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -23466,7 +23471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28617,6 +28622,28 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>161210</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Gaston</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>GAONA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
